--- a/data/chart/input/chart_89/辞工汇总表2024.xlsx
+++ b/data/chart/input/chart_89/辞工汇总表2024.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tianjiaojiao/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tianjiaojiao/Desktop/田姣姣/input/chart_89/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F9F6C3-CDE3-694D-A158-6B3C1E33EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEA7E69-3442-1846-AA7A-92FE2DBBD629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="22180" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="237">
   <si>
     <t>辞工汇总表</t>
   </si>
@@ -743,164 +743,15 @@
     <t>2024-01-04</t>
   </si>
   <si>
-    <t>张琳</t>
-  </si>
-  <si>
-    <t>赵峰</t>
-  </si>
-  <si>
-    <t>李琳</t>
-  </si>
-  <si>
-    <t>朱秀</t>
-  </si>
-  <si>
-    <t>杨雪</t>
-  </si>
-  <si>
-    <t>赵刚</t>
-  </si>
-  <si>
-    <t>高鑫</t>
-  </si>
-  <si>
-    <t>高静</t>
-  </si>
-  <si>
-    <t>陈超</t>
-  </si>
-  <si>
-    <t>赵鑫</t>
-  </si>
-  <si>
-    <t>徐超</t>
-  </si>
-  <si>
-    <t>郭静</t>
-  </si>
-  <si>
-    <t>朱杰</t>
-  </si>
-  <si>
-    <t>高博</t>
-  </si>
-  <si>
-    <t>马杰</t>
-  </si>
-  <si>
-    <t>杨浩</t>
-  </si>
-  <si>
-    <t>孙斌</t>
-  </si>
-  <si>
-    <t>罗超</t>
-  </si>
-  <si>
-    <t>黄文</t>
-  </si>
-  <si>
-    <t>徐浩</t>
-  </si>
-  <si>
-    <t>何磊</t>
-  </si>
-  <si>
-    <t>黄博</t>
-  </si>
-  <si>
-    <t>林超</t>
-  </si>
-  <si>
-    <t>杨宇</t>
-  </si>
-  <si>
-    <t>胡明</t>
-  </si>
-  <si>
-    <t>胡燕</t>
-  </si>
-  <si>
-    <t>陈文</t>
-  </si>
-  <si>
-    <t>吴鹏</t>
-  </si>
-  <si>
-    <t>高浩</t>
-  </si>
-  <si>
-    <t>何强</t>
-  </si>
-  <si>
-    <t>林博</t>
-  </si>
-  <si>
-    <t>孙明</t>
-  </si>
-  <si>
-    <t>刘浩</t>
-  </si>
-  <si>
-    <t>高涛</t>
-  </si>
-  <si>
-    <t>杨刚</t>
-  </si>
-  <si>
-    <t>王磊</t>
-  </si>
-  <si>
-    <t>罗勇</t>
-  </si>
-  <si>
-    <t>高勇</t>
-  </si>
-  <si>
-    <t>罗文</t>
-  </si>
-  <si>
-    <t>胡勇</t>
-  </si>
-  <si>
-    <t>吴斌</t>
-  </si>
-  <si>
-    <t>周伟</t>
-  </si>
-  <si>
-    <t>周萍</t>
-  </si>
-  <si>
-    <t>胡宇</t>
-  </si>
-  <si>
-    <t>赵斌</t>
-  </si>
-  <si>
-    <t>徐强</t>
-  </si>
-  <si>
-    <t>杨鹏</t>
-  </si>
-  <si>
-    <t>张强</t>
-  </si>
-  <si>
-    <t>王浩</t>
-  </si>
-  <si>
-    <t>高强</t>
-  </si>
-  <si>
-    <t>郭军</t>
+    <t>***</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -932,6 +783,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1003,7 +862,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1637,7 +1496,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>26</v>
@@ -1678,7 +1537,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -1719,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
@@ -1760,7 +1619,7 @@
         <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
@@ -1801,7 +1660,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>26</v>
@@ -1842,7 +1701,7 @@
         <v>54</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>26</v>
@@ -1883,7 +1742,7 @@
         <v>54</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
@@ -1924,7 +1783,7 @@
         <v>54</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>26</v>
@@ -1965,7 +1824,7 @@
         <v>54</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>26</v>
@@ -2006,7 +1865,7 @@
         <v>73</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
@@ -2047,7 +1906,7 @@
         <v>73</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>15</v>
@@ -2088,7 +1947,7 @@
         <v>73</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>26</v>
@@ -2129,7 +1988,7 @@
         <v>73</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>26</v>
@@ -2170,7 +2029,7 @@
         <v>73</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>26</v>
@@ -2211,7 +2070,7 @@
         <v>73</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>26</v>
@@ -2252,7 +2111,7 @@
         <v>73</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>26</v>
@@ -2293,7 +2152,7 @@
         <v>73</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>26</v>
@@ -2334,7 +2193,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>26</v>
@@ -2375,7 +2234,7 @@
         <v>73</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>26</v>
@@ -2416,7 +2275,7 @@
         <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
@@ -2457,7 +2316,7 @@
         <v>120</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>26</v>
@@ -2498,7 +2357,7 @@
         <v>120</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>26</v>
@@ -2539,7 +2398,7 @@
         <v>120</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>26</v>
@@ -2580,7 +2439,7 @@
         <v>120</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>26</v>
@@ -2621,7 +2480,7 @@
         <v>120</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>26</v>
@@ -2662,7 +2521,7 @@
         <v>120</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>15</v>
@@ -2703,7 +2562,7 @@
         <v>120</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>26</v>
@@ -2744,7 +2603,7 @@
         <v>120</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>26</v>
@@ -2785,7 +2644,7 @@
         <v>120</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>26</v>
@@ -2826,7 +2685,7 @@
         <v>150</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>26</v>
@@ -2867,7 +2726,7 @@
         <v>150</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>266</v>
+        <v>236</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>26</v>
@@ -2908,7 +2767,7 @@
         <v>150</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>26</v>
@@ -2949,7 +2808,7 @@
         <v>150</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>26</v>
@@ -2990,7 +2849,7 @@
         <v>150</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>26</v>
@@ -3031,7 +2890,7 @@
         <v>168</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>26</v>
@@ -3072,7 +2931,7 @@
         <v>168</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>271</v>
+        <v>236</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>26</v>
@@ -3113,7 +2972,7 @@
         <v>168</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>26</v>
@@ -3154,7 +3013,7 @@
         <v>168</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>26</v>
@@ -3195,7 +3054,7 @@
         <v>168</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>26</v>
@@ -3236,7 +3095,7 @@
         <v>168</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>26</v>
@@ -3277,7 +3136,7 @@
         <v>168</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>26</v>
@@ -3318,7 +3177,7 @@
         <v>168</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>26</v>
@@ -3359,7 +3218,7 @@
         <v>168</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>26</v>
@@ -3400,7 +3259,7 @@
         <v>200</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>15</v>
@@ -3441,7 +3300,7 @@
         <v>205</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>26</v>
@@ -3482,7 +3341,7 @@
         <v>205</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>26</v>
@@ -3523,7 +3382,7 @@
         <v>205</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>26</v>
@@ -3564,7 +3423,7 @@
         <v>216</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>282</v>
+        <v>236</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>26</v>
@@ -3605,7 +3464,7 @@
         <v>216</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>26</v>
@@ -3646,7 +3505,7 @@
         <v>216</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>26</v>
@@ -3687,7 +3546,7 @@
         <v>216</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>26</v>
@@ -3728,7 +3587,7 @@
         <v>216</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>26</v>
@@ -3769,7 +3628,7 @@
         <v>216</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>26</v>
@@ -4129,13 +3988,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DED1C7A8-C4BB-4304-A651-ADAA2BED2099}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8243539-448A-47C0-BF81-B36D6D77D231}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27C36AE6-85AF-491E-8E04-2EC9AE9795C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C288B480-C509-479B-836E-BB276F0D97C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08BC8A76-187C-4E72-AA93-88306A927CD0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9380AA10-967E-49A2-AAA8-4A0DC8DCC72F}"/>
 </file>